--- a/SGC-CKN/Excel/ed3cb78b-c967-4541-bcae-0acb35b8b1ee_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P341_D1200_31-03-2016.xlsx
+++ b/SGC-CKN/Excel/ed3cb78b-c967-4541-bcae-0acb35b8b1ee_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P341_D1200_31-03-2016.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>00:00 31/03/2016</t>
+    <t>00:00 31/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:10 31/03/2016</t>
+    <t>11:10 31/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -96,11 +96,11 @@
   </si>
   <si>
     <t xml:space="preserve">1:20
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:00
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t/>
@@ -113,7 +113,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:15
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -123,7 +123,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:00
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -133,7 +133,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:10
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -143,7 +143,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:30
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -153,7 +153,7 @@
   </si>
   <si>
     <t xml:space="preserve">06:00
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -163,7 +163,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:40
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -173,7 +173,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:25
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -183,7 +183,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:40
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -193,7 +193,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:55
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -203,7 +203,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:10
-31/3/2016</t>
+31/03/2026</t>
   </si>
   <si>
     <t>Độ sâu trước khi đổ bê tông: 75,41 (m)</t>
